--- a/education_forms/049_series_analysis_evaluation_quiz--education_forms.xlsx
+++ b/education_forms/049_series_analysis_evaluation_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,11 +776,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -826,19 +826,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>themes_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,24 +855,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>themes_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>reflection_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,304 +889,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>reflection_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>conclusion_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>conclusion_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>characters_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>themes_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>themes_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>themes_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>themes_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>themes_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>reflection_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>reflection_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>reflection_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>reflection_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>conclusion_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>conclusion_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
